--- a/bom/OSLUV_Excimer-Driver.xlsx
+++ b/bom/OSLUV_Excimer-Driver.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unsere_Geräte\Ushio Care222\OSLUV\09_Zeichnungen\Zeichnungen\KiCAD\OSLUV\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBB302B-A3F1-4FB3-8543-806B399ABB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63273E79-F9F3-4708-A91E-15A24FA01F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5715" yWindow="2655" windowWidth="21600" windowHeight="11280" xr2:uid="{68E81C6F-E3AF-44B4-92E9-C765077DD5C1}"/>
+    <workbookView xWindow="5340" yWindow="2475" windowWidth="21600" windowHeight="11295" xr2:uid="{68E81C6F-E3AF-44B4-92E9-C765077DD5C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>C42</t>
   </si>
   <si>
-    <t>10p 1% 600V 1206</t>
-  </si>
-  <si>
     <t>Capacitor_SMD:C_1206_3216Metric</t>
   </si>
   <si>
@@ -164,9 +161,6 @@
     <t>IC2</t>
   </si>
   <si>
-    <t>LM2901</t>
-  </si>
-  <si>
     <t>IC3</t>
   </si>
   <si>
@@ -179,9 +173,6 @@
     <t>IC4</t>
   </si>
   <si>
-    <t>INA210</t>
-  </si>
-  <si>
     <t>Package_TO_SOT_SMD:SOT-363_SC-70-6</t>
   </si>
   <si>
@@ -476,9 +467,6 @@
     <t>R67,R68</t>
   </si>
   <si>
-    <t>1Meg 0.1% 500V 1206</t>
-  </si>
-  <si>
     <t>12k 0.1% 0603</t>
   </si>
   <si>
@@ -561,9 +549,6 @@
   </si>
   <si>
     <t>KTR18EZPF1004</t>
-  </si>
-  <si>
-    <t>B59721A0070A062</t>
   </si>
   <si>
     <t>Component</t>
@@ -618,6 +603,21 @@
       </rPr>
       <t>≥1.9 W/mK. 24 x 22 mm. Acc. to drawing from 08.01.2026</t>
     </r>
+  </si>
+  <si>
+    <t>10p 1% 500V 1206</t>
+  </si>
+  <si>
+    <t>B59721A0080A062</t>
+  </si>
+  <si>
+    <t>1Meg 1% 500V 1206</t>
+  </si>
+  <si>
+    <t>INA210AIDCKJ</t>
+  </si>
+  <si>
+    <t>LM2901BIPWR</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1025,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1039,10 +1039,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B4">
         <v>14</v>
@@ -1064,16 +1064,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B5">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -1115,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>3</v>
@@ -1143,41 +1143,41 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D10" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E11" t="s">
         <v>16</v>
-      </c>
-      <c r="D11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
         <v>18</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1185,13 +1185,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
         <v>20</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1199,13 +1199,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
         <v>22</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1213,706 +1213,706 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" t="s">
         <v>25</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>178</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>26</v>
-      </c>
-      <c r="E18" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
         <v>28</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>29</v>
-      </c>
-      <c r="E19" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
         <v>32</v>
-      </c>
-      <c r="E21" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
       <c r="C22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
         <v>34</v>
-      </c>
-      <c r="E22" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" t="s">
         <v>36</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>179</v>
-      </c>
-      <c r="D24" t="s">
-        <v>159</v>
-      </c>
-      <c r="E24" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D25" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
         <v>39</v>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>40</v>
-      </c>
       <c r="E27" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>186</v>
       </c>
       <c r="E28" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" t="s">
         <v>43</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>185</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E33" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E36" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E37" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D39" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E39" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E41" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E42" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E43" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D45" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D48" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B50">
         <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E50" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E51" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B52">
         <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E53" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B54">
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E54" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D55" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E55" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E56" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E57" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E58" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E59" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E60" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E61" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E62" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E63" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E64" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E65" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E66" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="D67" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E67" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E68" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D69" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E69" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E70" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E71" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -1921,83 +1921,83 @@
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D73" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E73" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E74" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B76">
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E76" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E77" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D79" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E79" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
